--- a/exports/trend_1d/NAM-INDIA_full_report.xlsx
+++ b/exports/trend_1d/NAM-INDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.32</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H2" t="n">
-        <v>289.85</v>
+        <v>284.55</v>
       </c>
       <c r="I2" t="n">
         <v>288.5318061917562</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.91</v>
+        <v>2.01</v>
       </c>
       <c r="L2" t="n">
         <v>11.1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43286</v>
+        <v>43287</v>
       </c>
       <c r="H3" t="n">
-        <v>232.2</v>
+        <v>236.8</v>
       </c>
       <c r="I3" t="n">
         <v>235.9394483573982</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K3" t="n">
-        <v>18.4</v>
+        <v>16.78</v>
       </c>
       <c r="L3" t="n">
         <v>1.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H4" t="n">
-        <v>228.2</v>
+        <v>225.4</v>
       </c>
       <c r="I4" t="n">
         <v>228.0281635443328</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.63</v>
+        <v>-4.81</v>
       </c>
       <c r="L4" t="n">
         <v>8.779999999999999</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H5" t="n">
-        <v>172.5</v>
+        <v>182.05</v>
       </c>
       <c r="I5" t="n">
         <v>181.0510558097077</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K5" t="n">
-        <v>23.47</v>
+        <v>19.23</v>
       </c>
       <c r="L5" t="n">
         <v>2.04</v>
@@ -726,7 +785,7 @@
         <v>2.99</v>
       </c>
       <c r="N5" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="O5" t="n">
         <v>-1.23</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>16.54</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43458</v>
+        <v>43460</v>
       </c>
       <c r="H6" t="n">
-        <v>160.8</v>
+        <v>156.45</v>
       </c>
       <c r="I6" t="n">
         <v>159.0815758529493</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.67</v>
+        <v>-14.06</v>
       </c>
       <c r="L6" t="n">
-        <v>12.08</v>
+        <v>14.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.87</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.31</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H7" t="n">
-        <v>136.9</v>
+        <v>160.5</v>
       </c>
       <c r="I7" t="n">
         <v>147.2720431073361</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>12.5</v>
+        <v>-2.59</v>
       </c>
       <c r="L7" t="n">
         <v>4.76</v>
@@ -840,7 +923,7 @@
         <v>1.98</v>
       </c>
       <c r="N7" t="n">
-        <v>4.46</v>
+        <v>17.24</v>
       </c>
       <c r="O7" t="n">
         <v>-2.71</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>24.86</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43721</v>
+        <v>43724</v>
       </c>
       <c r="H8" t="n">
-        <v>262.25</v>
+        <v>248.85</v>
       </c>
       <c r="I8" t="n">
         <v>249.8680736228726</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K8" t="n">
-        <v>63.4</v>
+        <v>55.05</v>
       </c>
       <c r="L8" t="n">
         <v>16.88</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>16.51</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H9" t="n">
-        <v>265.7</v>
+        <v>273</v>
       </c>
       <c r="I9" t="n">
         <v>268.217837835787</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.77</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>10.39</v>
+        <v>10.41</v>
       </c>
       <c r="M9" t="n">
         <v>2.63</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>15.44</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43895</v>
+        <v>43896</v>
       </c>
       <c r="H10" t="n">
-        <v>385.25</v>
+        <v>344.3</v>
       </c>
       <c r="I10" t="n">
         <v>384.1325483825734</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K10" t="n">
-        <v>41.12</v>
+        <v>26.12</v>
       </c>
       <c r="L10" t="n">
         <v>4.93</v>
       </c>
       <c r="M10" t="n">
-        <v>3.54</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6.53</v>
+        <v>10.63</v>
       </c>
       <c r="O10" t="n">
         <v>2.75</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>19.98</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H11" t="n">
-        <v>270.05</v>
+        <v>277.3</v>
       </c>
       <c r="I11" t="n">
         <v>270.0586904638961</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="n">
-        <v>21.57</v>
+        <v>19.46</v>
       </c>
       <c r="L11" t="n">
         <v>3.05</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>15.15</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44036</v>
+        <v>44039</v>
       </c>
       <c r="H12" t="n">
-        <v>279.8</v>
+        <v>270.25</v>
       </c>
       <c r="I12" t="n">
         <v>279.64946169577</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9</v>
+        <v>-2.54</v>
       </c>
       <c r="L12" t="n">
         <v>7.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H13" t="n">
-        <v>278.6</v>
+        <v>285</v>
       </c>
       <c r="I13" t="n">
         <v>284.1723140724057</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.09</v>
+        <v>-5.46</v>
       </c>
       <c r="L13" t="n">
         <v>10.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H14" t="n">
-        <v>419.2</v>
+        <v>403.35</v>
       </c>
       <c r="I14" t="n">
         <v>411.9983033830011</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K14" t="n">
-        <v>47.09</v>
+        <v>41.53</v>
       </c>
       <c r="L14" t="n">
         <v>5.26</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>255</v>
+        <v>256</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.75</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H15" t="n">
-        <v>353.8</v>
+        <v>362.15</v>
       </c>
       <c r="I15" t="n">
         <v>360.3118485493612</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" t="n">
-        <v>12.28</v>
+        <v>10.21</v>
       </c>
       <c r="L15" t="n">
         <v>4.48</v>
@@ -1296,7 +1475,7 @@
         <v>1.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="O15" t="n">
         <v>-3.78</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.93</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H16" t="n">
-        <v>358.35</v>
+        <v>333.65</v>
       </c>
       <c r="I16" t="n">
         <v>343.9425506636646</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.05</v>
+        <v>-7.87</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2</v>
+        <v>8.52</v>
       </c>
       <c r="M16" t="n">
         <v>0.12</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>6.89</v>
       </c>
       <c r="O16" t="n">
         <v>2.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H17" t="n">
-        <v>315.85</v>
+        <v>335.7</v>
       </c>
       <c r="I17" t="n">
         <v>324.2718975859556</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" t="n">
-        <v>5.33</v>
+        <v>-0.61</v>
       </c>
       <c r="L17" t="n">
         <v>7.3</v>
@@ -1410,7 +1613,7 @@
         <v>2.43</v>
       </c>
       <c r="N17" t="n">
-        <v>4.14</v>
+        <v>6.28</v>
       </c>
       <c r="O17" t="n">
         <v>-6.89</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>13.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H18" t="n">
-        <v>331.6</v>
+        <v>320.3</v>
       </c>
       <c r="I18" t="n">
         <v>322.4011738153414</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.22</v>
+        <v>-4.59</v>
       </c>
       <c r="L18" t="n">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
       <c r="M18" t="n">
         <v>1.23</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.08</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H19" t="n">
-        <v>287.55</v>
+        <v>299.95</v>
       </c>
       <c r="I19" t="n">
         <v>295.8082477957238</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K19" t="n">
-        <v>10.22</v>
+        <v>6.35</v>
       </c>
       <c r="L19" t="n">
         <v>4.43</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H20" t="n">
-        <v>292.45</v>
+        <v>284.75</v>
       </c>
       <c r="I20" t="n">
         <v>286.1187785740425</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.5</v>
+        <v>-5.07</v>
       </c>
       <c r="L20" t="n">
         <v>9.199999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H21" t="n">
-        <v>210.05</v>
+        <v>215.8</v>
       </c>
       <c r="I21" t="n">
         <v>215.5087540120162</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K21" t="n">
-        <v>26.23</v>
+        <v>24.21</v>
       </c>
       <c r="L21" t="n">
         <v>3.21</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.67</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H22" t="n">
-        <v>493.9</v>
+        <v>445.2</v>
       </c>
       <c r="I22" t="n">
         <v>478.1091047950729</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K22" t="n">
-        <v>128.87</v>
+        <v>106.3</v>
       </c>
       <c r="L22" t="n">
         <v>2.57</v>
@@ -1695,7 +1958,7 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>4.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>2.74</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>235</v>
+        <v>236</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12</v>
+      </c>
+      <c r="U22" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>20.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H23" t="n">
-        <v>504.7</v>
+        <v>521.5</v>
       </c>
       <c r="I23" t="n">
         <v>514.4885855998908</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-13.36</v>
+        <v>-17.14</v>
       </c>
       <c r="L23" t="n">
-        <v>14.94</v>
+        <v>18.15</v>
       </c>
       <c r="M23" t="n">
         <v>1.67</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H24" t="n">
-        <v>623.7</v>
+        <v>546.4</v>
       </c>
       <c r="I24" t="n">
         <v>568.7327146146115</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K24" t="n">
-        <v>19.6</v>
+        <v>4.77</v>
       </c>
       <c r="L24" t="n">
         <v>4.08</v>
@@ -1809,7 +2096,7 @@
         <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>2.87</v>
+        <v>12.39</v>
       </c>
       <c r="O24" t="n">
         <v>3.33</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>20.55</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H25" t="n">
-        <v>611.7</v>
+        <v>648.95</v>
       </c>
       <c r="I25" t="n">
         <v>638.3425011621648</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.95</v>
+        <v>-18.77</v>
       </c>
       <c r="L25" t="n">
-        <v>15.12</v>
+        <v>20.24</v>
       </c>
       <c r="M25" t="n">
         <v>3.39</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>18.54</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H26" t="n">
-        <v>640.35</v>
+        <v>601.8</v>
       </c>
       <c r="I26" t="n">
         <v>605.7164993220761</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.33</v>
+        <v>-7.27</v>
       </c>
       <c r="L26" t="n">
         <v>10.69</v>
@@ -1923,7 +2234,7 @@
         <v>1.98</v>
       </c>
       <c r="N26" t="n">
-        <v>2.72</v>
+        <v>6.02</v>
       </c>
       <c r="O26" t="n">
         <v>6.09</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.9</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45520</v>
+        <v>45523</v>
       </c>
       <c r="H27" t="n">
-        <v>686.85</v>
+        <v>715.15</v>
       </c>
       <c r="I27" t="n">
         <v>695.0803071933734</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.13</v>
+        <v>-18.84</v>
       </c>
       <c r="L27" t="n">
-        <v>14.86</v>
+        <v>20.72</v>
       </c>
       <c r="M27" t="n">
         <v>2.95</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>13.93</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H28" t="n">
-        <v>659.25</v>
+        <v>631.05</v>
       </c>
       <c r="I28" t="n">
         <v>633.4744528584147</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.82</v>
+        <v>-11.76</v>
       </c>
       <c r="L28" t="n">
-        <v>10.54</v>
+        <v>12.19</v>
       </c>
       <c r="M28" t="n">
         <v>1.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.82</v>
+        <v>4.28</v>
       </c>
       <c r="O28" t="n">
         <v>4.12</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>15.42</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45580</v>
+        <v>45581</v>
       </c>
       <c r="H29" t="n">
-        <v>707.05</v>
+        <v>718.7</v>
       </c>
       <c r="I29" t="n">
         <v>708.8629458917069</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.04</v>
+        <v>-13.89</v>
       </c>
       <c r="L29" t="n">
-        <v>13.3</v>
+        <v>18.63</v>
       </c>
       <c r="M29" t="n">
         <v>2.3</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.04</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H30" t="n">
-        <v>722.75</v>
+        <v>701.5</v>
       </c>
       <c r="I30" t="n">
         <v>710.5247674269557</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.39</v>
       </c>
       <c r="L30" t="n">
         <v>8.859999999999999</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.92</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H31" t="n">
-        <v>563.1</v>
+        <v>590.25</v>
       </c>
       <c r="I31" t="n">
         <v>585.8747830011102</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>19.73</v>
+        <v>15.86</v>
       </c>
       <c r="L31" t="n">
         <v>3.52</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.56</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H32" t="n">
-        <v>798.5</v>
+        <v>784.75</v>
       </c>
       <c r="I32" t="n">
         <v>796.9893172576416</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K32" t="n">
-        <v>35.28</v>
+        <v>32.95</v>
       </c>
       <c r="L32" t="n">
         <v>15.62</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>11.61</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H33" t="n">
-        <v>855.9</v>
+        <v>871</v>
       </c>
       <c r="I33" t="n">
         <v>870.2691820472817</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.07</v>
+        <v>-10.99</v>
       </c>
       <c r="L33" t="n">
-        <v>9.720000000000001</v>
+        <v>12.04</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H34" t="n">
-        <v>904.95</v>
+        <v>857.9</v>
       </c>
       <c r="I34" t="n">
         <v>870.7657240779638</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>-1.5</v>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="M34" t="n">
-        <v>0.79</v>
+        <v>3.86</v>
       </c>
       <c r="N34" t="n">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.76</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.04</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="H35" t="n">
-        <v>865.05</v>
+        <v>915.65</v>
       </c>
       <c r="I35" t="n">
         <v>888.8028511469306</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.83</v>
+        <v>-6.73</v>
       </c>
       <c r="L35" t="n">
-        <v>4.54</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>0.83</v>
+        <v>1.84</v>
       </c>
       <c r="N35" t="n">
-        <v>5.09</v>
+        <v>5.85</v>
       </c>
       <c r="O35" t="n">
         <v>-5.2</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H36" t="n">
-        <v>842.75</v>
+        <v>823.95</v>
       </c>
       <c r="I36" t="n">
         <v>826.4689112327617</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.96</v>
+        <v>-10.01</v>
       </c>
       <c r="L36" t="n">
-        <v>9.57</v>
+        <v>10.71</v>
       </c>
       <c r="M36" t="n">
         <v>2.26</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>11.52</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H37" t="n">
-        <v>862.45</v>
+        <v>929</v>
       </c>
       <c r="I37" t="n">
         <v>894.3895090971312</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.67</v>
+        <v>-12.75</v>
       </c>
       <c r="L37" t="n">
-        <v>11.56</v>
+        <v>22.46</v>
       </c>
       <c r="M37" t="n">
-        <v>0.97</v>
+        <v>16.99</v>
       </c>
       <c r="N37" t="n">
-        <v>4.49</v>
+        <v>7.72</v>
       </c>
       <c r="O37" t="n">
         <v>-2.23</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>11.05</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H38" t="n">
-        <v>903.45</v>
+        <v>850.45</v>
       </c>
       <c r="I38" t="n">
         <v>867.7795810926731</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.75</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>3.92</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>3.24</v>
       </c>
       <c r="N38" t="n">
-        <v>5.49</v>
+        <v>5.87</v>
       </c>
       <c r="O38" t="n">
         <v>7.72</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H39" t="n">
-        <v>908.65</v>
+        <v>955.25</v>
       </c>
       <c r="I39" t="n">
         <v>916.3682247591482</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.84</v>
+        <v>-12.32</v>
       </c>
       <c r="L39" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="M39" t="n">
         <v>3.54</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.27</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H40" t="n">
-        <v>1147.9</v>
+        <v>1105.8</v>
       </c>
       <c r="I40" t="n">
         <v>1118.402217370055</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K40" t="n">
-        <v>20.17</v>
+        <v>15.76</v>
       </c>
       <c r="L40" t="n">
         <v>4.5</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.97</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H41" t="n">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="I41" t="n">
         <v>1214.280319808079</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>8.699999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H42" t="n">
-        <v>1189.6</v>
+        <v>1153.1</v>
       </c>
       <c r="I42" t="n">
         <v>1153.84765232879</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.09</v>
+        <v>-5.09</v>
       </c>
       <c r="L42" t="n">
         <v>5.61</v>
@@ -2835,7 +3338,7 @@
         <v>1.35</v>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>3.07</v>
       </c>
       <c r="O42" t="n">
         <v>1.08</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2895,6 +3410,14 @@
       <c r="Q43" t="n">
         <v>30</v>
       </c>
+      <c r="R43" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6697,7 +7220,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.8</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -6707,7 +7230,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -6717,7 +7240,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8">
@@ -6727,7 +7250,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -6737,7 +7260,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -6747,7 +7270,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -6757,7 +7280,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -6767,7 +7290,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -6777,7 +7300,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.3</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="14">
@@ -6787,7 +7310,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.289999999999999</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="15">
@@ -6797,7 +7320,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.37</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="16">
@@ -6807,7 +7330,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.91</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -6817,7 +7340,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128.87</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="18">
@@ -6827,7 +7350,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="19">
@@ -6837,7 +7360,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.79</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="20">
@@ -6847,7 +7370,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.54</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -6857,7 +7380,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.88</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="22">
@@ -6867,7 +7390,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6877,7 +7400,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -6887,7 +7410,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.48</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="25">
@@ -6897,7 +7420,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.75</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="26">
@@ -6907,7 +7430,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.43</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="27">
@@ -6917,7 +7440,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.46</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="28">
@@ -6927,7 +7450,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
